--- a/dataset/large/Surveillance_Drones_Large_Dataset.xlsx
+++ b/dataset/large/Surveillance_Drones_Large_Dataset.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdeva\OneDrive\Desktop\UATM\dataset\large\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3841A0CA-F90C-4428-BF3C-FEBF466E0702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="221">
   <si>
     <t>Drone_ID</t>
   </si>
@@ -128,13 +134,562 @@
   </si>
   <si>
     <t>South Bangalore</t>
+  </si>
+  <si>
+    <t>SRV_009</t>
+  </si>
+  <si>
+    <t>SRV_012</t>
+  </si>
+  <si>
+    <t>SRV_017</t>
+  </si>
+  <si>
+    <t>SRV_021</t>
+  </si>
+  <si>
+    <t>SRV_022</t>
+  </si>
+  <si>
+    <t>SRV_023</t>
+  </si>
+  <si>
+    <t>SRV_024</t>
+  </si>
+  <si>
+    <t>SRV_025</t>
+  </si>
+  <si>
+    <t>SRV_026</t>
+  </si>
+  <si>
+    <t>SRV_027</t>
+  </si>
+  <si>
+    <t>SRV_028</t>
+  </si>
+  <si>
+    <t>SRV_029</t>
+  </si>
+  <si>
+    <t>SRV_030</t>
+  </si>
+  <si>
+    <t>SRV_031</t>
+  </si>
+  <si>
+    <t>SRV_032</t>
+  </si>
+  <si>
+    <t>SRV_033</t>
+  </si>
+  <si>
+    <t>SRV_034</t>
+  </si>
+  <si>
+    <t>SRV_035</t>
+  </si>
+  <si>
+    <t>SRV_036</t>
+  </si>
+  <si>
+    <t>SRV_037</t>
+  </si>
+  <si>
+    <t>SRV_038</t>
+  </si>
+  <si>
+    <t>SRV_039</t>
+  </si>
+  <si>
+    <t>SRV_040</t>
+  </si>
+  <si>
+    <t>SRV_041</t>
+  </si>
+  <si>
+    <t>SRV_042</t>
+  </si>
+  <si>
+    <t>SRV_043</t>
+  </si>
+  <si>
+    <t>SRV_044</t>
+  </si>
+  <si>
+    <t>SRV_045</t>
+  </si>
+  <si>
+    <t>SRV_046</t>
+  </si>
+  <si>
+    <t>SRV_047</t>
+  </si>
+  <si>
+    <t>SRV_048</t>
+  </si>
+  <si>
+    <t>SRV_049</t>
+  </si>
+  <si>
+    <t>SRV_050</t>
+  </si>
+  <si>
+    <t>SRV_051</t>
+  </si>
+  <si>
+    <t>SRV_052</t>
+  </si>
+  <si>
+    <t>SRV_053</t>
+  </si>
+  <si>
+    <t>SRV_054</t>
+  </si>
+  <si>
+    <t>SRV_055</t>
+  </si>
+  <si>
+    <t>SRV_056</t>
+  </si>
+  <si>
+    <t>SRV_057</t>
+  </si>
+  <si>
+    <t>SRV_058</t>
+  </si>
+  <si>
+    <t>SRV_059</t>
+  </si>
+  <si>
+    <t>SRV_060</t>
+  </si>
+  <si>
+    <t>SRV_061</t>
+  </si>
+  <si>
+    <t>SRV_062</t>
+  </si>
+  <si>
+    <t>SRV_063</t>
+  </si>
+  <si>
+    <t>SRV_064</t>
+  </si>
+  <si>
+    <t>SRV_065</t>
+  </si>
+  <si>
+    <t>SRV_066</t>
+  </si>
+  <si>
+    <t>SRV_067</t>
+  </si>
+  <si>
+    <t>SRV_068</t>
+  </si>
+  <si>
+    <t>SRV_069</t>
+  </si>
+  <si>
+    <t>SRV_070</t>
+  </si>
+  <si>
+    <t>SRV_071</t>
+  </si>
+  <si>
+    <t>SRV_072</t>
+  </si>
+  <si>
+    <t>SRV_073</t>
+  </si>
+  <si>
+    <t>SRV_074</t>
+  </si>
+  <si>
+    <t>SRV_075</t>
+  </si>
+  <si>
+    <t>SRV_076</t>
+  </si>
+  <si>
+    <t>SRV_077</t>
+  </si>
+  <si>
+    <t>SRV_078</t>
+  </si>
+  <si>
+    <t>SRV_079</t>
+  </si>
+  <si>
+    <t>SRV_080</t>
+  </si>
+  <si>
+    <t>SRV_081</t>
+  </si>
+  <si>
+    <t>SRV_082</t>
+  </si>
+  <si>
+    <t>SRV_083</t>
+  </si>
+  <si>
+    <t>SRV_084</t>
+  </si>
+  <si>
+    <t>SRV_085</t>
+  </si>
+  <si>
+    <t>SRV_086</t>
+  </si>
+  <si>
+    <t>SRV_087</t>
+  </si>
+  <si>
+    <t>SRV_088</t>
+  </si>
+  <si>
+    <t>SRV_089</t>
+  </si>
+  <si>
+    <t>SRV_090</t>
+  </si>
+  <si>
+    <t>SRV_091</t>
+  </si>
+  <si>
+    <t>SRV_092</t>
+  </si>
+  <si>
+    <t>SRV_093</t>
+  </si>
+  <si>
+    <t>SRV_094</t>
+  </si>
+  <si>
+    <t>SRV_095</t>
+  </si>
+  <si>
+    <t>SRV_096</t>
+  </si>
+  <si>
+    <t>SRV_097</t>
+  </si>
+  <si>
+    <t>SRV_098</t>
+  </si>
+  <si>
+    <t>SRV_099</t>
+  </si>
+  <si>
+    <t>SRV_100</t>
+  </si>
+  <si>
+    <t>SRV_101</t>
+  </si>
+  <si>
+    <t>SRV_102</t>
+  </si>
+  <si>
+    <t>SRV_103</t>
+  </si>
+  <si>
+    <t>SRV_104</t>
+  </si>
+  <si>
+    <t>SRV_105</t>
+  </si>
+  <si>
+    <t>SRV_106</t>
+  </si>
+  <si>
+    <t>SRV_107</t>
+  </si>
+  <si>
+    <t>SRV_108</t>
+  </si>
+  <si>
+    <t>SRV_109</t>
+  </si>
+  <si>
+    <t>SRV_110</t>
+  </si>
+  <si>
+    <t>SRV_111</t>
+  </si>
+  <si>
+    <t>SRV_112</t>
+  </si>
+  <si>
+    <t>SRV_113</t>
+  </si>
+  <si>
+    <t>SRV_114</t>
+  </si>
+  <si>
+    <t>SRV_115</t>
+  </si>
+  <si>
+    <t>SRV_116</t>
+  </si>
+  <si>
+    <t>SRV_117</t>
+  </si>
+  <si>
+    <t>SRV_118</t>
+  </si>
+  <si>
+    <t>SRV_119</t>
+  </si>
+  <si>
+    <t>SRV_120</t>
+  </si>
+  <si>
+    <t>SRV_121</t>
+  </si>
+  <si>
+    <t>SRV_122</t>
+  </si>
+  <si>
+    <t>SRV_123</t>
+  </si>
+  <si>
+    <t>SRV_124</t>
+  </si>
+  <si>
+    <t>SRV_125</t>
+  </si>
+  <si>
+    <t>SRV_126</t>
+  </si>
+  <si>
+    <t>SRV_127</t>
+  </si>
+  <si>
+    <t>SRV_128</t>
+  </si>
+  <si>
+    <t>SRV_129</t>
+  </si>
+  <si>
+    <t>SRV_130</t>
+  </si>
+  <si>
+    <t>SRV_131</t>
+  </si>
+  <si>
+    <t>SRV_132</t>
+  </si>
+  <si>
+    <t>SRV_133</t>
+  </si>
+  <si>
+    <t>SRV_134</t>
+  </si>
+  <si>
+    <t>SRV_135</t>
+  </si>
+  <si>
+    <t>SRV_136</t>
+  </si>
+  <si>
+    <t>SRV_137</t>
+  </si>
+  <si>
+    <t>SRV_138</t>
+  </si>
+  <si>
+    <t>SRV_139</t>
+  </si>
+  <si>
+    <t>SRV_140</t>
+  </si>
+  <si>
+    <t>SRV_141</t>
+  </si>
+  <si>
+    <t>SRV_142</t>
+  </si>
+  <si>
+    <t>SRV_143</t>
+  </si>
+  <si>
+    <t>SRV_144</t>
+  </si>
+  <si>
+    <t>SRV_145</t>
+  </si>
+  <si>
+    <t>SRV_146</t>
+  </si>
+  <si>
+    <t>SRV_147</t>
+  </si>
+  <si>
+    <t>SRV_148</t>
+  </si>
+  <si>
+    <t>SRV_149</t>
+  </si>
+  <si>
+    <t>SRV_150</t>
+  </si>
+  <si>
+    <t>SRV_151</t>
+  </si>
+  <si>
+    <t>SRV_152</t>
+  </si>
+  <si>
+    <t>SRV_153</t>
+  </si>
+  <si>
+    <t>SRV_154</t>
+  </si>
+  <si>
+    <t>SRV_155</t>
+  </si>
+  <si>
+    <t>SRV_156</t>
+  </si>
+  <si>
+    <t>SRV_157</t>
+  </si>
+  <si>
+    <t>SRV_158</t>
+  </si>
+  <si>
+    <t>SRV_159</t>
+  </si>
+  <si>
+    <t>SRV_160</t>
+  </si>
+  <si>
+    <t>SRV_161</t>
+  </si>
+  <si>
+    <t>SRV_162</t>
+  </si>
+  <si>
+    <t>SRV_163</t>
+  </si>
+  <si>
+    <t>SRV_164</t>
+  </si>
+  <si>
+    <t>SRV_165</t>
+  </si>
+  <si>
+    <t>SRV_166</t>
+  </si>
+  <si>
+    <t>SRV_167</t>
+  </si>
+  <si>
+    <t>SRV_168</t>
+  </si>
+  <si>
+    <t>SRV_169</t>
+  </si>
+  <si>
+    <t>SRV_170</t>
+  </si>
+  <si>
+    <t>SRV_171</t>
+  </si>
+  <si>
+    <t>SRV_172</t>
+  </si>
+  <si>
+    <t>SRV_173</t>
+  </si>
+  <si>
+    <t>SRV_174</t>
+  </si>
+  <si>
+    <t>SRV_175</t>
+  </si>
+  <si>
+    <t>SRV_176</t>
+  </si>
+  <si>
+    <t>SRV_177</t>
+  </si>
+  <si>
+    <t>SRV_178</t>
+  </si>
+  <si>
+    <t>SRV_179</t>
+  </si>
+  <si>
+    <t>SRV_180</t>
+  </si>
+  <si>
+    <t>SRV_181</t>
+  </si>
+  <si>
+    <t>SRV_182</t>
+  </si>
+  <si>
+    <t>SRV_183</t>
+  </si>
+  <si>
+    <t>SRV_184</t>
+  </si>
+  <si>
+    <t>SRV_185</t>
+  </si>
+  <si>
+    <t>SRV_186</t>
+  </si>
+  <si>
+    <t>SRV_187</t>
+  </si>
+  <si>
+    <t>SRV_188</t>
+  </si>
+  <si>
+    <t>SRV_189</t>
+  </si>
+  <si>
+    <t>SRV_190</t>
+  </si>
+  <si>
+    <t>SRV_191</t>
+  </si>
+  <si>
+    <t>SRV_192</t>
+  </si>
+  <si>
+    <t>SRV_193</t>
+  </si>
+  <si>
+    <t>SRV_194</t>
+  </si>
+  <si>
+    <t>SRV_195</t>
+  </si>
+  <si>
+    <t>SRV_196</t>
+  </si>
+  <si>
+    <t>SRV_197</t>
+  </si>
+  <si>
+    <t>SRV_198</t>
+  </si>
+  <si>
+    <t>SRV_199</t>
+  </si>
+  <si>
+    <t>SRV_200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +701,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -197,13 +758,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -241,7 +810,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -275,6 +844,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -309,9 +879,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,11 +1055,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,9 +1094,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>85.75</v>
@@ -549,15 +1120,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>17.84</v>
       </c>
       <c r="C3">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D3">
         <v>63.97</v>
@@ -575,18 +1146,18 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>14.53</v>
       </c>
       <c r="C4">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D4">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -601,7 +1172,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -627,9 +1198,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>59.57</v>
@@ -638,7 +1209,7 @@
         <v>78.14</v>
       </c>
       <c r="D6">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -653,9 +1224,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>45.76</v>
@@ -670,7 +1241,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H7" t="s">
         <v>34</v>
@@ -679,15 +1250,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>4.34</v>
       </c>
       <c r="C8">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D8">
         <v>41.75</v>
@@ -705,9 +1276,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>85.75</v>
@@ -731,9 +1302,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>63.73</v>
@@ -748,7 +1319,7 @@
         <v>31</v>
       </c>
       <c r="F10">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H10" t="s">
         <v>35</v>
@@ -757,9 +1328,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>85.75</v>
@@ -783,9 +1354,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>85.75</v>
@@ -809,15 +1380,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B13">
         <v>17.84</v>
       </c>
       <c r="C13">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D13">
         <v>63.97</v>
@@ -835,15 +1406,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>4.34</v>
       </c>
       <c r="C14">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D14">
         <v>41.75</v>
@@ -861,9 +1432,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>33.94</v>
@@ -872,7 +1443,7 @@
         <v>27.52</v>
       </c>
       <c r="D15">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -887,12 +1458,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C16">
         <v>57.37</v>
@@ -913,9 +1484,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>59.57</v>
@@ -924,7 +1495,7 @@
         <v>78.14</v>
       </c>
       <c r="D17">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -939,9 +1510,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B18">
         <v>33.94</v>
@@ -950,7 +1521,7 @@
         <v>27.52</v>
       </c>
       <c r="D18">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -965,9 +1536,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>33.94</v>
@@ -976,7 +1547,7 @@
         <v>27.52</v>
       </c>
       <c r="D19">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -991,9 +1562,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>16.72</v>
@@ -1017,9 +1588,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>45.76</v>
@@ -1034,7 +1605,7 @@
         <v>28</v>
       </c>
       <c r="F21">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H21" t="s">
         <v>34</v>
@@ -1043,9 +1614,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B22">
         <v>85.75</v>
@@ -1069,9 +1640,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B23">
         <v>85.75</v>
@@ -1095,9 +1666,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B24">
         <v>85.75</v>
@@ -1121,15 +1692,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B25">
         <v>4.34</v>
       </c>
       <c r="C25">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D25">
         <v>41.75</v>
@@ -1147,9 +1718,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B26">
         <v>85.75</v>
@@ -1173,9 +1744,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>16.72</v>
@@ -1199,15 +1770,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B28">
         <v>17.84</v>
       </c>
       <c r="C28">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D28">
         <v>63.97</v>
@@ -1225,9 +1796,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B29">
         <v>16.72</v>
@@ -1251,9 +1822,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B30">
         <v>74.19</v>
@@ -1277,9 +1848,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B31">
         <v>74.91</v>
@@ -1288,7 +1859,7 @@
         <v>18.36</v>
       </c>
       <c r="D31">
-        <v>18.24</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="E31" t="s">
         <v>32</v>
@@ -1303,15 +1874,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B32">
         <v>55.43</v>
       </c>
       <c r="C32">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D32">
         <v>91.94</v>
@@ -1329,9 +1900,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="B33">
         <v>59.57</v>
@@ -1340,7 +1911,7 @@
         <v>78.14</v>
       </c>
       <c r="D33">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E33" t="s">
         <v>29</v>
@@ -1355,12 +1926,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="B34">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C34">
         <v>57.37</v>
@@ -1381,9 +1952,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B35">
         <v>63.73</v>
@@ -1398,7 +1969,7 @@
         <v>31</v>
       </c>
       <c r="F35">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H35" t="s">
         <v>35</v>
@@ -1407,9 +1978,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B36">
         <v>45.76</v>
@@ -1424,7 +1995,7 @@
         <v>28</v>
       </c>
       <c r="F36">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H36" t="s">
         <v>34</v>
@@ -1433,15 +2004,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B37">
         <v>17.84</v>
       </c>
       <c r="C37">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D37">
         <v>63.97</v>
@@ -1459,9 +2030,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B38">
         <v>69.16</v>
@@ -1485,9 +2056,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="B39">
         <v>45.76</v>
@@ -1502,7 +2073,7 @@
         <v>28</v>
       </c>
       <c r="F39">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H39" t="s">
         <v>34</v>
@@ -1511,15 +2082,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B40">
         <v>55.43</v>
       </c>
       <c r="C40">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D40">
         <v>91.94</v>
@@ -1537,9 +2108,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B41">
         <v>69.16</v>
@@ -1563,9 +2134,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B42">
         <v>74.91</v>
@@ -1574,7 +2145,7 @@
         <v>18.36</v>
       </c>
       <c r="D42">
-        <v>18.24</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="E42" t="s">
         <v>32</v>
@@ -1589,9 +2160,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B43">
         <v>85.75</v>
@@ -1615,9 +2186,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="B44">
         <v>85.75</v>
@@ -1641,15 +2212,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B45">
         <v>55.43</v>
       </c>
       <c r="C45">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D45">
         <v>91.94</v>
@@ -1667,9 +2238,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="B46">
         <v>45.76</v>
@@ -1684,7 +2255,7 @@
         <v>28</v>
       </c>
       <c r="F46">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H46" t="s">
         <v>34</v>
@@ -1693,9 +2264,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="B47">
         <v>63.73</v>
@@ -1710,7 +2281,7 @@
         <v>31</v>
       </c>
       <c r="F47">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H47" t="s">
         <v>35</v>
@@ -1719,15 +2290,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="B48">
         <v>17.84</v>
       </c>
       <c r="C48">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D48">
         <v>63.97</v>
@@ -1745,9 +2316,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="B49">
         <v>16.72</v>
@@ -1771,15 +2342,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="B50">
         <v>17.84</v>
       </c>
       <c r="C50">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D50">
         <v>63.97</v>
@@ -1797,9 +2368,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="B51">
         <v>85.75</v>
@@ -1823,15 +2394,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B52">
         <v>4.34</v>
       </c>
       <c r="C52">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D52">
         <v>41.75</v>
@@ -1849,9 +2420,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B53">
         <v>85.75</v>
@@ -1875,15 +2446,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="B54">
         <v>17.84</v>
       </c>
       <c r="C54">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D54">
         <v>63.97</v>
@@ -1901,12 +2472,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="B55">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C55">
         <v>57.37</v>
@@ -1927,9 +2498,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="B56">
         <v>69.16</v>
@@ -1953,9 +2524,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="B57">
         <v>45.76</v>
@@ -1970,7 +2541,7 @@
         <v>28</v>
       </c>
       <c r="F57">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H57" t="s">
         <v>34</v>
@@ -1979,15 +2550,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="B58">
         <v>55.43</v>
       </c>
       <c r="C58">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D58">
         <v>91.94</v>
@@ -2005,18 +2576,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="B59">
         <v>14.53</v>
       </c>
       <c r="C59">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D59">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E59" t="s">
         <v>29</v>
@@ -2031,9 +2602,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="B60">
         <v>28.85</v>
@@ -2057,9 +2628,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="B61">
         <v>45.76</v>
@@ -2074,7 +2645,7 @@
         <v>28</v>
       </c>
       <c r="F61">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H61" t="s">
         <v>34</v>
@@ -2083,9 +2654,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="B62">
         <v>59.57</v>
@@ -2094,7 +2665,7 @@
         <v>78.14</v>
       </c>
       <c r="D62">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E62" t="s">
         <v>29</v>
@@ -2109,9 +2680,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="B63">
         <v>16.72</v>
@@ -2135,9 +2706,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="B64">
         <v>16.72</v>
@@ -2161,9 +2732,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="B65">
         <v>69.16</v>
@@ -2187,18 +2758,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="B66">
         <v>14.53</v>
       </c>
       <c r="C66">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D66">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E66" t="s">
         <v>29</v>
@@ -2213,9 +2784,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="B67">
         <v>28.85</v>
@@ -2239,15 +2810,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="B68">
         <v>17.84</v>
       </c>
       <c r="C68">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D68">
         <v>63.97</v>
@@ -2265,9 +2836,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="B69">
         <v>74.91</v>
@@ -2276,7 +2847,7 @@
         <v>18.36</v>
       </c>
       <c r="D69">
-        <v>18.24</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="E69" t="s">
         <v>32</v>
@@ -2291,9 +2862,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="B70">
         <v>69.16</v>
@@ -2317,9 +2888,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="B71">
         <v>28.85</v>
@@ -2343,9 +2914,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="B72">
         <v>74.19</v>
@@ -2369,9 +2940,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="B73">
         <v>59.57</v>
@@ -2380,7 +2951,7 @@
         <v>78.14</v>
       </c>
       <c r="D73">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E73" t="s">
         <v>29</v>
@@ -2395,9 +2966,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="B74">
         <v>16.72</v>
@@ -2421,9 +2992,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="B75">
         <v>16.72</v>
@@ -2447,9 +3018,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="B76">
         <v>28.85</v>
@@ -2473,9 +3044,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B77">
         <v>74.19</v>
@@ -2499,9 +3070,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="B78">
         <v>29.96</v>
@@ -2525,15 +3096,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="B79">
         <v>17.84</v>
       </c>
       <c r="C79">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D79">
         <v>63.97</v>
@@ -2551,9 +3122,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="B80">
         <v>85.75</v>
@@ -2577,9 +3148,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="B81">
         <v>29.96</v>
@@ -2603,15 +3174,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="B82">
         <v>17.84</v>
       </c>
       <c r="C82">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D82">
         <v>63.97</v>
@@ -2629,9 +3200,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="B83">
         <v>16.72</v>
@@ -2655,9 +3226,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="B84">
         <v>45.76</v>
@@ -2672,7 +3243,7 @@
         <v>28</v>
       </c>
       <c r="F84">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H84" t="s">
         <v>34</v>
@@ -2681,9 +3252,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="B85">
         <v>85.75</v>
@@ -2707,9 +3278,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="B86">
         <v>85.75</v>
@@ -2733,9 +3304,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="B87">
         <v>59.57</v>
@@ -2744,7 +3315,7 @@
         <v>78.14</v>
       </c>
       <c r="D87">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E87" t="s">
         <v>29</v>
@@ -2759,15 +3330,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="B88">
         <v>17.84</v>
       </c>
       <c r="C88">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D88">
         <v>63.97</v>
@@ -2785,15 +3356,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="B89">
         <v>55.43</v>
       </c>
       <c r="C89">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D89">
         <v>91.94</v>
@@ -2811,9 +3382,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="B90">
         <v>33.94</v>
@@ -2822,7 +3393,7 @@
         <v>27.52</v>
       </c>
       <c r="D90">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -2837,9 +3408,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="B91">
         <v>45.76</v>
@@ -2854,7 +3425,7 @@
         <v>28</v>
       </c>
       <c r="F91">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H91" t="s">
         <v>34</v>
@@ -2863,9 +3434,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="B92">
         <v>59.57</v>
@@ -2874,7 +3445,7 @@
         <v>78.14</v>
       </c>
       <c r="D92">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E92" t="s">
         <v>29</v>
@@ -2889,9 +3460,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="B93">
         <v>85.75</v>
@@ -2915,15 +3486,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="B94">
         <v>17.84</v>
       </c>
       <c r="C94">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D94">
         <v>63.97</v>
@@ -2941,9 +3512,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="B95">
         <v>59.57</v>
@@ -2952,7 +3523,7 @@
         <v>78.14</v>
       </c>
       <c r="D95">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E95" t="s">
         <v>29</v>
@@ -2967,9 +3538,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="B96">
         <v>30.37</v>
@@ -2993,12 +3564,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="B97">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C97">
         <v>57.37</v>
@@ -3019,15 +3590,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="B98">
         <v>4.34</v>
       </c>
       <c r="C98">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D98">
         <v>41.75</v>
@@ -3045,9 +3616,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="B99">
         <v>45.76</v>
@@ -3062,7 +3633,7 @@
         <v>28</v>
       </c>
       <c r="F99">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H99" t="s">
         <v>34</v>
@@ -3071,9 +3642,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="B100">
         <v>69.16</v>
@@ -3097,9 +3668,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="B101">
         <v>69.16</v>
@@ -3123,9 +3694,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="B102">
         <v>63.73</v>
@@ -3140,7 +3711,7 @@
         <v>31</v>
       </c>
       <c r="F102">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H102" t="s">
         <v>35</v>
@@ -3149,9 +3720,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="B103">
         <v>85.75</v>
@@ -3175,9 +3746,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="B104">
         <v>59.57</v>
@@ -3186,7 +3757,7 @@
         <v>78.14</v>
       </c>
       <c r="D104">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E104" t="s">
         <v>29</v>
@@ -3201,15 +3772,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="B105">
         <v>17.84</v>
       </c>
       <c r="C105">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D105">
         <v>63.97</v>
@@ -3227,9 +3798,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="B106">
         <v>45.76</v>
@@ -3244,7 +3815,7 @@
         <v>28</v>
       </c>
       <c r="F106">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H106" t="s">
         <v>34</v>
@@ -3253,15 +3824,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="B107">
         <v>55.43</v>
       </c>
       <c r="C107">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D107">
         <v>91.94</v>
@@ -3279,18 +3850,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="B108">
         <v>14.53</v>
       </c>
       <c r="C108">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D108">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E108" t="s">
         <v>29</v>
@@ -3305,9 +3876,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="B109">
         <v>74.19</v>
@@ -3331,9 +3902,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="B110">
         <v>59.57</v>
@@ -3342,7 +3913,7 @@
         <v>78.14</v>
       </c>
       <c r="D110">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E110" t="s">
         <v>29</v>
@@ -3357,9 +3928,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="B111">
         <v>59.57</v>
@@ -3368,7 +3939,7 @@
         <v>78.14</v>
       </c>
       <c r="D111">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E111" t="s">
         <v>29</v>
@@ -3383,9 +3954,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="B112">
         <v>59.57</v>
@@ -3394,7 +3965,7 @@
         <v>78.14</v>
       </c>
       <c r="D112">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E112" t="s">
         <v>29</v>
@@ -3409,15 +3980,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="B113">
         <v>4.34</v>
       </c>
       <c r="C113">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D113">
         <v>41.75</v>
@@ -3435,15 +4006,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="B114">
         <v>55.43</v>
       </c>
       <c r="C114">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D114">
         <v>91.94</v>
@@ -3461,9 +4032,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="B115">
         <v>45.76</v>
@@ -3478,7 +4049,7 @@
         <v>28</v>
       </c>
       <c r="F115">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H115" t="s">
         <v>34</v>
@@ -3487,9 +4058,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="B116">
         <v>59.57</v>
@@ -3498,7 +4069,7 @@
         <v>78.14</v>
       </c>
       <c r="D116">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E116" t="s">
         <v>29</v>
@@ -3513,15 +4084,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="B117">
         <v>4.34</v>
       </c>
       <c r="C117">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D117">
         <v>41.75</v>
@@ -3539,9 +4110,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="B118">
         <v>59.57</v>
@@ -3550,7 +4121,7 @@
         <v>78.14</v>
       </c>
       <c r="D118">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E118" t="s">
         <v>29</v>
@@ -3565,9 +4136,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="B119">
         <v>69.16</v>
@@ -3591,12 +4162,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="B120">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C120">
         <v>57.37</v>
@@ -3617,15 +4188,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="B121">
         <v>4.34</v>
       </c>
       <c r="C121">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D121">
         <v>41.75</v>
@@ -3643,15 +4214,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="B122">
         <v>55.43</v>
       </c>
       <c r="C122">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D122">
         <v>91.94</v>
@@ -3669,9 +4240,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="B123">
         <v>59.57</v>
@@ -3680,7 +4251,7 @@
         <v>78.14</v>
       </c>
       <c r="D123">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E123" t="s">
         <v>29</v>
@@ -3695,9 +4266,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="B124">
         <v>29.96</v>
@@ -3721,12 +4292,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="B125">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C125">
         <v>57.37</v>
@@ -3747,9 +4318,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="B126">
         <v>29.96</v>
@@ -3773,9 +4344,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="B127">
         <v>63.73</v>
@@ -3790,7 +4361,7 @@
         <v>31</v>
       </c>
       <c r="F127">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H127" t="s">
         <v>35</v>
@@ -3799,9 +4370,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="B128">
         <v>69.16</v>
@@ -3825,15 +4396,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="B129">
         <v>17.84</v>
       </c>
       <c r="C129">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D129">
         <v>63.97</v>
@@ -3851,12 +4422,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="B130">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C130">
         <v>57.37</v>
@@ -3877,9 +4448,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="B131">
         <v>59.57</v>
@@ -3888,7 +4459,7 @@
         <v>78.14</v>
       </c>
       <c r="D131">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E131" t="s">
         <v>29</v>
@@ -3903,15 +4474,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="B132">
         <v>55.43</v>
       </c>
       <c r="C132">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D132">
         <v>91.94</v>
@@ -3929,9 +4500,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="B133">
         <v>16.72</v>
@@ -3955,15 +4526,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="B134">
         <v>17.84</v>
       </c>
       <c r="C134">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D134">
         <v>63.97</v>
@@ -3981,9 +4552,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="B135">
         <v>29.96</v>
@@ -4007,15 +4578,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="B136">
         <v>4.34</v>
       </c>
       <c r="C136">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D136">
         <v>41.75</v>
@@ -4033,15 +4604,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="B137">
         <v>4.34</v>
       </c>
       <c r="C137">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D137">
         <v>41.75</v>
@@ -4059,15 +4630,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="B138">
         <v>55.43</v>
       </c>
       <c r="C138">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D138">
         <v>91.94</v>
@@ -4085,9 +4656,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B139">
         <v>45.76</v>
@@ -4102,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="F139">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H139" t="s">
         <v>34</v>
@@ -4111,15 +4682,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="B140">
         <v>17.84</v>
       </c>
       <c r="C140">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D140">
         <v>63.97</v>
@@ -4137,15 +4708,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="B141">
         <v>17.84</v>
       </c>
       <c r="C141">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D141">
         <v>63.97</v>
@@ -4163,15 +4734,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="B142">
         <v>17.84</v>
       </c>
       <c r="C142">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D142">
         <v>63.97</v>
@@ -4189,15 +4760,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="B143">
         <v>4.34</v>
       </c>
       <c r="C143">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D143">
         <v>41.75</v>
@@ -4215,18 +4786,18 @@
         <v>108</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="B144">
         <v>14.53</v>
       </c>
       <c r="C144">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D144">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E144" t="s">
         <v>29</v>
@@ -4241,9 +4812,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="B145">
         <v>45.76</v>
@@ -4258,7 +4829,7 @@
         <v>28</v>
       </c>
       <c r="F145">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H145" t="s">
         <v>34</v>
@@ -4267,15 +4838,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B146">
         <v>17.84</v>
       </c>
       <c r="C146">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D146">
         <v>63.97</v>
@@ -4293,9 +4864,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="B147">
         <v>85.75</v>
@@ -4319,15 +4890,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="B148">
         <v>17.84</v>
       </c>
       <c r="C148">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D148">
         <v>63.97</v>
@@ -4345,9 +4916,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="B149">
         <v>85.75</v>
@@ -4371,18 +4942,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="B150">
         <v>14.53</v>
       </c>
       <c r="C150">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D150">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E150" t="s">
         <v>29</v>
@@ -4397,12 +4968,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="B151">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C151">
         <v>57.37</v>
@@ -4423,9 +4994,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>22</v>
+        <v>171</v>
       </c>
       <c r="B152">
         <v>74.91</v>
@@ -4434,7 +5005,7 @@
         <v>18.36</v>
       </c>
       <c r="D152">
-        <v>18.24</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="E152" t="s">
         <v>32</v>
@@ -4449,15 +5020,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="B153">
         <v>17.84</v>
       </c>
       <c r="C153">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D153">
         <v>63.97</v>
@@ -4475,9 +5046,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="B154">
         <v>63.73</v>
@@ -4492,7 +5063,7 @@
         <v>31</v>
       </c>
       <c r="F154">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H154" t="s">
         <v>35</v>
@@ -4501,9 +5072,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="B155">
         <v>29.96</v>
@@ -4527,15 +5098,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="B156">
         <v>55.43</v>
       </c>
       <c r="C156">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D156">
         <v>91.94</v>
@@ -4553,15 +5124,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="B157">
         <v>55.43</v>
       </c>
       <c r="C157">
-        <v>67.43000000000001</v>
+        <v>67.430000000000007</v>
       </c>
       <c r="D157">
         <v>91.94</v>
@@ -4579,9 +5150,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="B158">
         <v>16.72</v>
@@ -4605,9 +5176,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="B159">
         <v>59.57</v>
@@ -4616,7 +5187,7 @@
         <v>78.14</v>
       </c>
       <c r="D159">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E159" t="s">
         <v>29</v>
@@ -4631,18 +5202,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
       <c r="B160">
         <v>14.53</v>
       </c>
       <c r="C160">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D160">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E160" t="s">
         <v>29</v>
@@ -4657,9 +5228,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="B161">
         <v>33.94</v>
@@ -4668,7 +5239,7 @@
         <v>27.52</v>
       </c>
       <c r="D161">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -4683,18 +5254,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="B162">
         <v>14.53</v>
       </c>
       <c r="C162">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D162">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E162" t="s">
         <v>29</v>
@@ -4709,9 +5280,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="B163">
         <v>74.19</v>
@@ -4735,9 +5306,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>16</v>
+        <v>183</v>
       </c>
       <c r="B164">
         <v>45.76</v>
@@ -4752,7 +5323,7 @@
         <v>28</v>
       </c>
       <c r="F164">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H164" t="s">
         <v>34</v>
@@ -4761,9 +5332,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="B165">
         <v>59.57</v>
@@ -4772,7 +5343,7 @@
         <v>78.14</v>
       </c>
       <c r="D165">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E165" t="s">
         <v>29</v>
@@ -4787,9 +5358,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="B166">
         <v>33.94</v>
@@ -4798,7 +5369,7 @@
         <v>27.52</v>
       </c>
       <c r="D166">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -4813,15 +5384,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>12</v>
+        <v>186</v>
       </c>
       <c r="B167">
         <v>17.84</v>
       </c>
       <c r="C167">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D167">
         <v>63.97</v>
@@ -4839,9 +5410,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="B168">
         <v>69.16</v>
@@ -4865,9 +5436,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="B169">
         <v>69.16</v>
@@ -4891,18 +5462,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="B170">
         <v>14.53</v>
       </c>
       <c r="C170">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D170">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E170" t="s">
         <v>29</v>
@@ -4917,18 +5488,18 @@
         <v>99</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="B171">
         <v>14.53</v>
       </c>
       <c r="C171">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D171">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E171" t="s">
         <v>29</v>
@@ -4943,9 +5514,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="B172">
         <v>74.19</v>
@@ -4969,15 +5540,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="B173">
         <v>17.84</v>
       </c>
       <c r="C173">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D173">
         <v>63.97</v>
@@ -4995,12 +5566,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B174">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C174">
         <v>57.37</v>
@@ -5021,15 +5592,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="B175">
         <v>4.34</v>
       </c>
       <c r="C175">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D175">
         <v>41.75</v>
@@ -5047,12 +5618,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="B176">
-        <v>87.76000000000001</v>
+        <v>87.76</v>
       </c>
       <c r="C176">
         <v>57.37</v>
@@ -5073,9 +5644,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>16</v>
+        <v>196</v>
       </c>
       <c r="B177">
         <v>45.76</v>
@@ -5090,7 +5661,7 @@
         <v>28</v>
       </c>
       <c r="F177">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H177" t="s">
         <v>34</v>
@@ -5099,15 +5670,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="B178">
         <v>17.84</v>
       </c>
       <c r="C178">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D178">
         <v>63.97</v>
@@ -5125,9 +5696,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="B179">
         <v>85.75</v>
@@ -5151,9 +5722,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="B180">
         <v>33.94</v>
@@ -5162,7 +5733,7 @@
         <v>27.52</v>
       </c>
       <c r="D180">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -5177,9 +5748,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="B181">
         <v>59.57</v>
@@ -5188,7 +5759,7 @@
         <v>78.14</v>
       </c>
       <c r="D181">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E181" t="s">
         <v>29</v>
@@ -5203,9 +5774,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>15</v>
+        <v>201</v>
       </c>
       <c r="B182">
         <v>59.57</v>
@@ -5214,7 +5785,7 @@
         <v>78.14</v>
       </c>
       <c r="D182">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E182" t="s">
         <v>29</v>
@@ -5229,9 +5800,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>11</v>
+        <v>202</v>
       </c>
       <c r="B183">
         <v>85.75</v>
@@ -5255,9 +5826,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="B184">
         <v>45.76</v>
@@ -5272,7 +5843,7 @@
         <v>28</v>
       </c>
       <c r="F184">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H184" t="s">
         <v>34</v>
@@ -5281,9 +5852,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="B185">
         <v>85.75</v>
@@ -5307,9 +5878,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="B186">
         <v>59.57</v>
@@ -5318,7 +5889,7 @@
         <v>78.14</v>
       </c>
       <c r="D186">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E186" t="s">
         <v>29</v>
@@ -5333,9 +5904,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="B187">
         <v>45.76</v>
@@ -5350,7 +5921,7 @@
         <v>28</v>
       </c>
       <c r="F187">
-        <v>76.40000000000001</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="H187" t="s">
         <v>34</v>
@@ -5359,9 +5930,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="B188">
         <v>33.94</v>
@@ -5370,7 +5941,7 @@
         <v>27.52</v>
       </c>
       <c r="D188">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -5385,18 +5956,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>13</v>
+        <v>208</v>
       </c>
       <c r="B189">
         <v>14.53</v>
       </c>
       <c r="C189">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D189">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E189" t="s">
         <v>29</v>
@@ -5411,9 +5982,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>15</v>
+        <v>209</v>
       </c>
       <c r="B190">
         <v>59.57</v>
@@ -5422,7 +5993,7 @@
         <v>78.14</v>
       </c>
       <c r="D190">
-        <v>68.26000000000001</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="E190" t="s">
         <v>29</v>
@@ -5437,9 +6008,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="B191">
         <v>16.72</v>
@@ -5463,15 +6034,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>12</v>
+        <v>211</v>
       </c>
       <c r="B192">
         <v>17.84</v>
       </c>
       <c r="C192">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D192">
         <v>63.97</v>
@@ -5489,9 +6060,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="B193">
         <v>69.16</v>
@@ -5515,18 +6086,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>13</v>
+        <v>213</v>
       </c>
       <c r="B194">
         <v>14.53</v>
       </c>
       <c r="C194">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D194">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E194" t="s">
         <v>29</v>
@@ -5541,9 +6112,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="B195">
         <v>63.73</v>
@@ -5558,7 +6129,7 @@
         <v>31</v>
       </c>
       <c r="F195">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H195" t="s">
         <v>35</v>
@@ -5567,15 +6138,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="B196">
         <v>4.34</v>
       </c>
       <c r="C196">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="D196">
         <v>41.75</v>
@@ -5593,18 +6164,18 @@
         <v>108</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>13</v>
+        <v>216</v>
       </c>
       <c r="B197">
         <v>14.53</v>
       </c>
       <c r="C197">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="D197">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E197" t="s">
         <v>29</v>
@@ -5619,15 +6190,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>12</v>
+        <v>217</v>
       </c>
       <c r="B198">
         <v>17.84</v>
       </c>
       <c r="C198">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D198">
         <v>63.97</v>
@@ -5645,9 +6216,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="B199">
         <v>63.73</v>
@@ -5662,7 +6233,7 @@
         <v>31</v>
       </c>
       <c r="F199">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="H199" t="s">
         <v>35</v>
@@ -5671,9 +6242,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="B200">
         <v>85.75</v>
@@ -5697,15 +6268,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>12</v>
+        <v>220</v>
       </c>
       <c r="B201">
         <v>17.84</v>
       </c>
       <c r="C201">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D201">
         <v>63.97</v>
@@ -5724,6 +6295,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/dataset/large/Surveillance_Drones_Large_Dataset.xlsx
+++ b/dataset/large/Surveillance_Drones_Large_Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdeva\OneDrive\Desktop\UATM\dataset\large\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74f3fc933c58b622/Desktop/UATM/dataset/large/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3841A0CA-F90C-4428-BF3C-FEBF466E0702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3841A0CA-F90C-4428-BF3C-FEBF466E0702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8D3B1CF-5933-4280-AA5C-55276378C7C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1058,6 +1058,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K201"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="14.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
